--- a/artfynd/A 56897-2021 artfynd.xlsx
+++ b/artfynd/A 56897-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,116 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114702868</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57179</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102620</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Surnia ulula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långvik, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>570068</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6536225</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ingrid Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ingrid Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56897-2021 artfynd.xlsx
+++ b/artfynd/A 56897-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56897-2021 artfynd.xlsx
+++ b/artfynd/A 56897-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,6 +1014,139 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115015188</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57186</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102620</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Surnia ulula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långvik, syd Djulönäs (Långvik, syd Djulönäs), Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570025</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6536109</v>
+      </c>
+      <c r="S5" t="n">
+        <v>30</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sitter väl synlig i en björk vid vägen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Agneta Sundkvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Agneta Sundkvist, Hans Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56897-2021 artfynd.xlsx
+++ b/artfynd/A 56897-2021 artfynd.xlsx
@@ -795,11 +795,11 @@
         <v>114510727</v>
       </c>
       <c r="B3" t="n">
-        <v>57212</v>
+        <v>57321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -909,11 +909,11 @@
         <v>114702868</v>
       </c>
       <c r="B4" t="n">
-        <v>57212</v>
+        <v>57321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1019,11 +1019,11 @@
         <v>115015188</v>
       </c>
       <c r="B5" t="n">
-        <v>57212</v>
+        <v>57321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1068,7 +1068,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långvik, syd Djulönäs (Långvik, syd Djulönäs), Srm</t>
+          <t>Långvik, syd Djulönäs, Långvik, syd Djulönäs, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">

--- a/artfynd/A 56897-2021 artfynd.xlsx
+++ b/artfynd/A 56897-2021 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>114510727</v>
       </c>
       <c r="B3" t="n">
-        <v>57321</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>114702868</v>
       </c>
       <c r="B4" t="n">
-        <v>57321</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>115015188</v>
       </c>
       <c r="B5" t="n">
-        <v>57321</v>
+        <v>57326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 56897-2021 artfynd.xlsx
+++ b/artfynd/A 56897-2021 artfynd.xlsx
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agneta Sundkvist, Hans Andersson</t>
+          <t>Hans Andersson, Agneta Sundkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 56897-2021 artfynd.xlsx
+++ b/artfynd/A 56897-2021 artfynd.xlsx
@@ -810,11 +810,6 @@
       <c r="E3" t="n">
         <v>102620</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Hökuggla</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Surnia ulula</t>
@@ -924,11 +919,6 @@
       <c r="E4" t="n">
         <v>102620</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Hökuggla</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Surnia ulula</t>
@@ -1034,11 +1024,6 @@
       <c r="E5" t="n">
         <v>102620</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Hökuggla</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Surnia ulula</t>
@@ -1142,7 +1127,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Andersson, Agneta Sundkvist</t>
+          <t>Agneta Sundkvist, Hans Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 56897-2021 artfynd.xlsx
+++ b/artfynd/A 56897-2021 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>114510727</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>57330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,6 +809,11 @@
       </c>
       <c r="E3" t="n">
         <v>102620</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -904,7 +909,7 @@
         <v>114702868</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>57330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,6 +923,11 @@
       </c>
       <c r="E4" t="n">
         <v>102620</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1009,7 +1019,7 @@
         <v>115015188</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>57330</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,6 +1033,11 @@
       </c>
       <c r="E5" t="n">
         <v>102620</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 56897-2021 artfynd.xlsx
+++ b/artfynd/A 56897-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5030134</v>
+        <v>97330390</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>St.Malm, Långviksnäset, Srm</t>
+          <t>Katrineholm, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570437.87848733</v>
+        <v>570280</v>
       </c>
       <c r="R2" t="n">
-        <v>6536117.477016715</v>
+        <v>6536267</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-04-03</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-04-03</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,21 +771,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>hassellund</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,16 +790,11 @@
         <v>114510727</v>
       </c>
       <c r="B3" t="n">
-        <v>57425</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -909,16 +899,11 @@
         <v>114702868</v>
       </c>
       <c r="B4" t="n">
-        <v>57425</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1019,16 +1004,11 @@
         <v>115015188</v>
       </c>
       <c r="B5" t="n">
-        <v>57425</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1146,6 +1126,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5030134</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>St.Malm, Långviksnäset, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>570438</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6536117</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2007-04-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2007-04-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>hassellund</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56897-2021 artfynd.xlsx
+++ b/artfynd/A 56897-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330390</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114510727</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114702868</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115015188</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,8 +1253,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5030134</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>